--- a/SCENARIOS/SCENARIO 4/Simulation Results/AStar 10 Agents Benchmarking_2026-04-17_03-02-35.xlsx
+++ b/SCENARIOS/SCENARIO 4/Simulation Results/AStar 10 Agents Benchmarking_2026-04-17_03-02-35.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\SCENARIOS\SCENARIO 4\Simulation Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50090332-86EE-408F-8ABD-F267B8E43B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82805289-0607-474B-8A01-D5FE6F5762FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
-    <sheet name="ActiveGoals" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
-    <sheet name="AStar 10 Agents Benchmarking 2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
+    <sheet name="ActiveGoals" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
+    <sheet name="AStar 10 Agents Benchmarking 2" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runs!$A$1:$P$59</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="142">
   <si>
     <t>Run</t>
   </si>
@@ -436,12 +437,45 @@
   <si>
     <t>% Average</t>
   </si>
+  <si>
+    <t>Σενάριο</t>
+  </si>
+  <si>
+    <t>Αλγόριθμος εύρεσης διαδρομής</t>
+  </si>
+  <si>
+    <t>Α*</t>
+  </si>
+  <si>
+    <t>D*Lite</t>
+  </si>
+  <si>
+    <t>Λαμβάνεται υπόψιν η διασπορά του αερίου στην εύρεση της βέλτιστης διαδρομής</t>
+  </si>
+  <si>
+    <t>û</t>
+  </si>
+  <si>
+    <t>ü</t>
+  </si>
+  <si>
+    <t>Στατική εύρεση διαδρομής</t>
+  </si>
+  <si>
+    <t>Δυναμική εύρεση διαδρομής</t>
+  </si>
+  <si>
+    <t>Χρησιμοποιήθηκε το pathfinding του Agents.jl</t>
+  </si>
+  <si>
+    <t>Χρησιμοποιήθηκε νέος κώδικας που αναπτύχθηκε</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -456,6 +490,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FFFF0000"/>
+      <name val="Wingdings"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF00B050"/>
+      <name val="Wingdings"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -465,7 +520,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -473,15 +528,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7276,15 +7362,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6490D35-F7BC-4AAC-B3CF-9E427C5FC2AA}">
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S59"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="36.19921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.19921875" customWidth="1"/>
     <col min="18" max="19" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7322,7 +7408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7359,8 +7445,12 @@
       <c r="P2">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="S2" s="3">
+        <f>H2/10</f>
+        <v>1.1424999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>3</v>
       </c>
@@ -7397,8 +7487,12 @@
       <c r="P3">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="S3" s="3">
+        <f>H3/10</f>
+        <v>0.22399999999999939</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7436,7 +7530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>6</v>
       </c>
@@ -7474,7 +7568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>7</v>
       </c>
@@ -7509,7 +7603,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -7547,7 +7641,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>4</v>
       </c>
@@ -7585,7 +7679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7620,7 +7714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>16</v>
       </c>
@@ -7655,7 +7749,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>12</v>
       </c>
@@ -7690,7 +7784,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>9</v>
       </c>
@@ -7725,7 +7819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>13</v>
       </c>
@@ -7760,7 +7854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19">
       <c r="A14">
         <v>15</v>
       </c>
@@ -7795,7 +7889,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19">
       <c r="A15">
         <v>10</v>
       </c>
@@ -7830,7 +7924,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19">
       <c r="A16">
         <v>14</v>
       </c>
@@ -7865,7 +7959,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>17</v>
       </c>
@@ -7900,7 +7994,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>18</v>
       </c>
@@ -7935,7 +8029,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>11</v>
       </c>
@@ -7970,7 +8064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8005,7 +8099,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>22</v>
       </c>
@@ -8040,7 +8134,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>24</v>
       </c>
@@ -8075,7 +8169,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>29</v>
       </c>
@@ -8110,7 +8204,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>26</v>
       </c>
@@ -8145,7 +8239,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>27</v>
       </c>
@@ -8180,7 +8274,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>30</v>
       </c>
@@ -8215,7 +8309,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>21</v>
       </c>
@@ -8250,7 +8344,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>33</v>
       </c>
@@ -8285,7 +8379,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>23</v>
       </c>
@@ -8320,7 +8414,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>20</v>
       </c>
@@ -8355,7 +8449,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>28</v>
       </c>
@@ -8390,7 +8484,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>25</v>
       </c>
@@ -8425,7 +8519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>34</v>
       </c>
@@ -8460,7 +8554,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>32</v>
       </c>
@@ -8495,7 +8589,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>31</v>
       </c>
@@ -8530,7 +8624,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>36</v>
       </c>
@@ -8565,7 +8659,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>37</v>
       </c>
@@ -8600,7 +8694,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>41</v>
       </c>
@@ -8635,7 +8729,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8670,7 +8764,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>35</v>
       </c>
@@ -8705,7 +8799,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>39</v>
       </c>
@@ -8740,7 +8834,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>43</v>
       </c>
@@ -8775,7 +8869,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>45</v>
       </c>
@@ -8810,7 +8904,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>44</v>
       </c>
@@ -8845,7 +8939,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>42</v>
       </c>
@@ -8880,7 +8974,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>40</v>
       </c>
@@ -8915,7 +9009,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>48</v>
       </c>
@@ -8950,7 +9044,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>50</v>
       </c>
@@ -8985,7 +9079,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>46</v>
       </c>
@@ -9020,7 +9114,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>47</v>
       </c>
@@ -9055,7 +9149,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>49</v>
       </c>
@@ -9090,7 +9184,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -9098,7 +9192,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
         <v>113</v>
       </c>
@@ -9106,7 +9200,7 @@
         <v>48.177255904000006</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -9114,7 +9208,7 @@
         <v>284.12705062200001</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
         <v>115</v>
       </c>
@@ -9122,7 +9216,7 @@
         <v>332.304306526</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
         <v>116</v>
       </c>
@@ -9130,7 +9224,7 @@
         <v>8.384298399999994E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
         <v>117</v>
       </c>
@@ -9138,7 +9232,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
         <v>118</v>
       </c>
@@ -9146,7 +9240,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -9166,9 +9260,145 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2A73431-D09C-434A-AE53-E0F024A64499}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="52.19921875" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="60.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="5.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="31.8" thickBot="1">
+      <c r="A1" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="5">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="63" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="94.2" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="31.8" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="31.8" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="63" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="63" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68994187-0F56-447D-A270-0041890E7641}">
   <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="21.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.19921875" customWidth="1"/>
@@ -9180,7 +9410,7 @@
     <col min="17" max="17" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -9215,7 +9445,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -9258,7 +9488,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -9301,7 +9531,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -9344,7 +9574,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -9387,7 +9617,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -9430,7 +9660,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -9473,7 +9703,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -9516,7 +9746,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -9559,7 +9789,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -9602,7 +9832,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -9645,7 +9875,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -9688,7 +9918,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -9731,7 +9961,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -9774,7 +10004,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -9817,7 +10047,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -9860,7 +10090,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -9903,7 +10133,7 @@
         <v>0.36125000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -9911,7 +10141,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -9920,7 +10150,7 @@
       </c>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -9928,7 +10158,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -9936,7 +10166,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -9944,7 +10174,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -9952,7 +10182,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -9960,7 +10190,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -9968,7 +10198,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -9976,7 +10206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -9984,7 +10214,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -9992,7 +10222,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -10000,7 +10230,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -10008,7 +10238,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -10016,7 +10246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -10024,7 +10254,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -10032,7 +10262,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -10040,7 +10270,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -10048,7 +10278,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -10056,7 +10286,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -10064,7 +10294,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -10072,7 +10302,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -10080,7 +10310,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -10088,7 +10318,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -10096,7 +10326,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -10104,7 +10334,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -10112,7 +10342,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -10120,7 +10350,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -10128,7 +10358,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -10136,7 +10366,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -10144,7 +10374,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -10152,7 +10382,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -10160,7 +10390,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -10168,552 +10398,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>108</v>
       </c>
       <c r="B51" t="s">
         <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91309D74-E8A3-4350-A9F3-55B12A1CC1DD}">
-  <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="11.19921875"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>11.424999999999997</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>11.424999999999997</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <f>Sheet1!$D$2/5</f>
-        <v>2.2849999999999993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>6.7349999999999852</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4.4874999999999901</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <f>D3/5</f>
-        <v>0.89749999999999797</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2.239999999999994</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>3.0439999999999885</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H8" si="0">D4/5</f>
-        <v>0.60879999999999768</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>6.3749999999999707</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>2.6359090909090868</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>0.52718181818181731</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2.3500000000000014</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>1.1736666666666653</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>0.23473333333333307</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>0.78227272727272534</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>11</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>0.15645454545454507</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>0.25200000000000011</v>
-      </c>
-      <c r="E8">
-        <v>8</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>5.0400000000000021E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>6.494999999999969</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>0.94500000000000073</v>
-      </c>
-      <c r="B10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>4.2750000000000012</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="D12">
-        <v>0.21000000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>0.82500000000000051</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <v>0.39000000000000024</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1.4600000000000011</v>
-      </c>
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>0.66000000000000036</v>
-      </c>
-      <c r="E15">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>1.8950000000000014</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>0</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>3.6300000000000003</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>3.9450000000000003</v>
-      </c>
-      <c r="B19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>6.0199999999999516</v>
-      </c>
-      <c r="B20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>0.95000000000000062</v>
-      </c>
-      <c r="B21">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>0.73000000000000043</v>
-      </c>
-      <c r="B22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>0</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>0.80500000000000049</v>
-      </c>
-      <c r="B24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>0</v>
-      </c>
-      <c r="B25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>2.0150000000000015</v>
-      </c>
-      <c r="B26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>0.27500000000000013</v>
-      </c>
-      <c r="B27">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>0.58000000000000029</v>
-      </c>
-      <c r="B28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>1.1750000000000007</v>
-      </c>
-      <c r="B29">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>0</v>
-      </c>
-      <c r="B30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>0.60000000000000042</v>
-      </c>
-      <c r="B31">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>4.620000000000001</v>
-      </c>
-      <c r="B32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>2.6699999999999955</v>
-      </c>
-      <c r="B33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>0.77000000000000046</v>
-      </c>
-      <c r="B34">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>2.4149999999999778</v>
-      </c>
-      <c r="B35">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>0.09</v>
-      </c>
-      <c r="B36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>0</v>
-      </c>
-      <c r="B37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>0</v>
-      </c>
-      <c r="B38">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="B39">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>0.41500000000000026</v>
-      </c>
-      <c r="B40">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>2.959999999999984</v>
-      </c>
-      <c r="B41">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="B42">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>2.1349999999999936</v>
-      </c>
-      <c r="B43">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>0.87500000000000044</v>
-      </c>
-      <c r="B44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>1.0750000000000006</v>
-      </c>
-      <c r="B45">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>0.98000000000000065</v>
-      </c>
-      <c r="B46">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>0.21000000000000005</v>
-      </c>
-      <c r="B47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>0.39000000000000024</v>
-      </c>
-      <c r="B48">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>0</v>
-      </c>
-      <c r="B49">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>0.66000000000000036</v>
-      </c>
-      <c r="B50">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>0</v>
-      </c>
-      <c r="B51">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10723,11 +10413,551 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91309D74-E8A3-4350-A9F3-55B12A1CC1DD}">
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="2" width="11.19921875"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
+        <v>11.424999999999997</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>11.424999999999997</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>Sheet1!$D$2/5</f>
+        <v>2.2849999999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>6.7349999999999852</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4.4874999999999901</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <f>D3/5</f>
+        <v>0.89749999999999797</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>2.239999999999994</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>3.0439999999999885</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H8" si="0">D4/5</f>
+        <v>0.60879999999999768</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>6.3749999999999707</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>2.6359090909090868</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>0.52718181818181731</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>2.3500000000000014</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>1.1736666666666653</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0.23473333333333307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>0.78227272727272534</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0.15645454545454507</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>0.25200000000000011</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>5.0400000000000021E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>6.494999999999969</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>0.94500000000000073</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>4.2750000000000012</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>0.21000000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>0.82500000000000051</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>0.39000000000000024</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>1.4600000000000011</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>0.66000000000000036</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>1.8950000000000014</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>3.6300000000000003</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>3.9450000000000003</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>6.0199999999999516</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>0.95000000000000062</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>0.73000000000000043</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>0.80500000000000049</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>2.0150000000000015</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>0.27500000000000013</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>0.58000000000000029</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>1.1750000000000007</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>0.60000000000000042</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>4.620000000000001</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>2.6699999999999955</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>0.77000000000000046</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>2.4149999999999778</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>0.09</v>
+      </c>
+      <c r="B36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>0.41500000000000026</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>2.959999999999984</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>2.1349999999999936</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>0.87500000000000044</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>1.0750000000000006</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>0.98000000000000065</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>0.21000000000000005</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>0.39000000000000024</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>0.66000000000000036</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD9DBD2-262E-467C-A39F-777C6FF38076}">
   <dimension ref="A1:D501"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>121</v>
       </c>
@@ -10741,7 +10971,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10755,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10769,7 +10999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10783,7 +11013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10797,7 +11027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -10811,7 +11041,7 @@
         <v>1.2150000000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -10825,7 +11055,7 @@
         <v>1.3550000000000009</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -10839,7 +11069,7 @@
         <v>1.7999999999999956</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -10853,7 +11083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -10867,7 +11097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>1</v>
       </c>
@@ -10881,7 +11111,7 @@
         <v>1.0550000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>3</v>
       </c>
@@ -10895,7 +11125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>3</v>
       </c>
@@ -10909,7 +11139,7 @@
         <v>0.11000000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>3</v>
       </c>
@@ -10923,7 +11153,7 @@
         <v>0.17500000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>3</v>
       </c>
@@ -10937,7 +11167,7 @@
         <v>0.64500000000000046</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>3</v>
       </c>
@@ -10951,7 +11181,7 @@
         <v>1.264999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>3</v>
       </c>
@@ -10965,7 +11195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>3</v>
       </c>
@@ -10979,7 +11209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>3</v>
       </c>
@@ -10993,7 +11223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>3</v>
       </c>
@@ -11007,7 +11237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>3</v>
       </c>
@@ -11021,7 +11251,7 @@
         <v>1.5399999999999892</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>3</v>
       </c>
@@ -11035,7 +11265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>3</v>
       </c>
@@ -11049,7 +11279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>3</v>
       </c>
@@ -11063,7 +11293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>3</v>
       </c>
@@ -11077,7 +11307,7 @@
         <v>1.3399999999999934</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>3</v>
       </c>
@@ -11091,7 +11321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>3</v>
       </c>
@@ -11105,7 +11335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>3</v>
       </c>
@@ -11119,7 +11349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>3</v>
       </c>
@@ -11133,7 +11363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>3</v>
       </c>
@@ -11147,7 +11377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>3</v>
       </c>
@@ -11161,7 +11391,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>4</v>
       </c>
@@ -11175,7 +11405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>4</v>
       </c>
@@ -11189,7 +11419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>4</v>
       </c>
@@ -11203,7 +11433,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>4</v>
       </c>
@@ -11217,7 +11447,7 @@
         <v>0.96500000000000064</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>4</v>
       </c>
@@ -11231,7 +11461,7 @@
         <v>1.0399999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>4</v>
       </c>
@@ -11245,7 +11475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>4</v>
       </c>
@@ -11259,7 +11489,7 @@
         <v>0.87000000000000066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>4</v>
       </c>
@@ -11273,7 +11503,7 @@
         <v>0.4650000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>4</v>
       </c>
@@ -11287,7 +11517,7 @@
         <v>2.4749999999999694</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>4</v>
       </c>
@@ -11301,7 +11531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>4</v>
       </c>
@@ -11315,7 +11545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>4</v>
       </c>
@@ -11329,7 +11559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>4</v>
       </c>
@@ -11343,7 +11573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>4</v>
       </c>
@@ -11357,7 +11587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>4</v>
       </c>
@@ -11371,7 +11601,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>4</v>
       </c>
@@ -11385,7 +11615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>4</v>
       </c>
@@ -11399,7 +11629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49">
         <v>4</v>
       </c>
@@ -11413,7 +11643,7 @@
         <v>1.2800000000000009</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50">
         <v>4</v>
       </c>
@@ -11427,7 +11657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51">
         <v>4</v>
       </c>
@@ -11441,7 +11671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52">
         <v>4</v>
       </c>
@@ -11455,7 +11685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="A53">
         <v>4</v>
       </c>
@@ -11469,7 +11699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="A54">
         <v>4</v>
       </c>
@@ -11483,7 +11713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55">
         <v>4</v>
       </c>
@@ -11497,7 +11727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56">
         <v>4</v>
       </c>
@@ -11511,7 +11741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57">
         <v>4</v>
       </c>
@@ -11525,7 +11755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58">
         <v>4</v>
       </c>
@@ -11539,7 +11769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="A59">
         <v>4</v>
       </c>
@@ -11553,7 +11783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="A60">
         <v>4</v>
       </c>
@@ -11567,7 +11797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="A61">
         <v>4</v>
       </c>
@@ -11581,7 +11811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="A62">
         <v>4</v>
       </c>
@@ -11595,7 +11825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4">
       <c r="A63">
         <v>4</v>
       </c>
@@ -11609,7 +11839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="A64">
         <v>4</v>
       </c>
@@ -11623,7 +11853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>4</v>
       </c>
@@ -11637,7 +11867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>4</v>
       </c>
@@ -11651,7 +11881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>4</v>
       </c>
@@ -11665,7 +11895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>4</v>
       </c>
@@ -11679,7 +11909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4">
       <c r="A69">
         <v>4</v>
       </c>
@@ -11693,7 +11923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4">
       <c r="A70">
         <v>4</v>
       </c>
@@ -11707,7 +11937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>4</v>
       </c>
@@ -11721,7 +11951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>4</v>
       </c>
@@ -11735,7 +11965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>4</v>
       </c>
@@ -11749,7 +11979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>4</v>
       </c>
@@ -11763,7 +11993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>4</v>
       </c>
@@ -11777,7 +12007,7 @@
         <v>1.6749999999999863</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>4</v>
       </c>
@@ -11791,7 +12021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>4</v>
       </c>
@@ -11805,7 +12035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4">
       <c r="A78">
         <v>4</v>
       </c>
@@ -11819,7 +12049,7 @@
         <v>1.8199999999999832</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>4</v>
       </c>
@@ -11833,7 +12063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>4</v>
       </c>
@@ -11847,7 +12077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4">
       <c r="A81">
         <v>4</v>
       </c>
@@ -11861,7 +12091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4">
       <c r="A82">
         <v>5</v>
       </c>
@@ -11875,7 +12105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4">
       <c r="A83">
         <v>5</v>
       </c>
@@ -11889,7 +12119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4">
       <c r="A84">
         <v>5</v>
       </c>
@@ -11903,7 +12133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4">
       <c r="A85">
         <v>5</v>
       </c>
@@ -11917,7 +12147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4">
       <c r="A86">
         <v>5</v>
       </c>
@@ -11931,7 +12161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4">
       <c r="A87">
         <v>5</v>
       </c>
@@ -11945,7 +12175,7 @@
         <v>0.94500000000000073</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4">
       <c r="A88">
         <v>5</v>
       </c>
@@ -11959,7 +12189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4">
       <c r="A89">
         <v>5</v>
       </c>
@@ -11973,7 +12203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4">
       <c r="A90">
         <v>5</v>
       </c>
@@ -11987,7 +12217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4">
       <c r="A91">
         <v>5</v>
       </c>
@@ -12001,7 +12231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4">
       <c r="A92">
         <v>5</v>
       </c>
@@ -12015,7 +12245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4">
       <c r="A93">
         <v>5</v>
       </c>
@@ -12029,7 +12259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4">
       <c r="A94">
         <v>5</v>
       </c>
@@ -12043,7 +12273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4">
       <c r="A95">
         <v>5</v>
       </c>
@@ -12057,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4">
       <c r="A96">
         <v>5</v>
       </c>
@@ -12071,7 +12301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4">
       <c r="A97">
         <v>5</v>
       </c>
@@ -12085,7 +12315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4">
       <c r="A98">
         <v>5</v>
       </c>
@@ -12099,7 +12329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4">
       <c r="A99">
         <v>5</v>
       </c>
@@ -12113,7 +12343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4">
       <c r="A100">
         <v>5</v>
       </c>
@@ -12127,7 +12357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4">
       <c r="A101">
         <v>5</v>
       </c>
@@ -12141,7 +12371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4">
       <c r="A102">
         <v>5</v>
       </c>
@@ -12155,7 +12385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4">
       <c r="A103">
         <v>5</v>
       </c>
@@ -12169,7 +12399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4">
       <c r="A104">
         <v>5</v>
       </c>
@@ -12183,7 +12413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4">
       <c r="A105">
         <v>5</v>
       </c>
@@ -12197,7 +12427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4">
       <c r="A106">
         <v>5</v>
       </c>
@@ -12211,7 +12441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4">
       <c r="A107">
         <v>5</v>
       </c>
@@ -12225,7 +12455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4">
       <c r="A108">
         <v>5</v>
       </c>
@@ -12239,7 +12469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4">
       <c r="A109">
         <v>5</v>
       </c>
@@ -12253,7 +12483,7 @@
         <v>0.98500000000000076</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4">
       <c r="A110">
         <v>5</v>
       </c>
@@ -12267,7 +12497,7 @@
         <v>0.29000000000000015</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4">
       <c r="A111">
         <v>5</v>
       </c>
@@ -12281,7 +12511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4">
       <c r="A112">
         <v>5</v>
       </c>
@@ -12295,7 +12525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4">
       <c r="A113">
         <v>5</v>
       </c>
@@ -12309,7 +12539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4">
       <c r="A114">
         <v>5</v>
       </c>
@@ -12323,7 +12553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4">
       <c r="A115">
         <v>5</v>
       </c>
@@ -12337,7 +12567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4">
       <c r="A116">
         <v>5</v>
       </c>
@@ -12351,7 +12581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4">
       <c r="A117">
         <v>5</v>
       </c>
@@ -12365,7 +12595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4">
       <c r="A118">
         <v>5</v>
       </c>
@@ -12379,7 +12609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4">
       <c r="A119">
         <v>5</v>
       </c>
@@ -12393,7 +12623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4">
       <c r="A120">
         <v>5</v>
       </c>
@@ -12407,7 +12637,7 @@
         <v>0.82500000000000051</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4">
       <c r="A121">
         <v>5</v>
       </c>
@@ -12421,7 +12651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4">
       <c r="A122">
         <v>5</v>
       </c>
@@ -12435,7 +12665,7 @@
         <v>0.70500000000000052</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4">
       <c r="A123">
         <v>5</v>
       </c>
@@ -12449,7 +12679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4">
       <c r="A124">
         <v>5</v>
       </c>
@@ -12463,7 +12693,7 @@
         <v>0.75500000000000056</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4">
       <c r="A125">
         <v>5</v>
       </c>
@@ -12477,7 +12707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4">
       <c r="A126">
         <v>5</v>
       </c>
@@ -12491,7 +12721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4">
       <c r="A127">
         <v>5</v>
       </c>
@@ -12505,7 +12735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4">
       <c r="A128">
         <v>5</v>
       </c>
@@ -12519,7 +12749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4">
       <c r="A129">
         <v>5</v>
       </c>
@@ -12533,7 +12763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4">
       <c r="A130">
         <v>5</v>
       </c>
@@ -12547,7 +12777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4">
       <c r="A131">
         <v>5</v>
       </c>
@@ -12561,7 +12791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4">
       <c r="A132">
         <v>5</v>
       </c>
@@ -12575,7 +12805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4">
       <c r="A133">
         <v>5</v>
       </c>
@@ -12589,7 +12819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4">
       <c r="A134">
         <v>5</v>
       </c>
@@ -12603,7 +12833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4">
       <c r="A135">
         <v>5</v>
       </c>
@@ -12617,7 +12847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4">
       <c r="A136">
         <v>5</v>
       </c>
@@ -12631,7 +12861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4">
       <c r="A137">
         <v>5</v>
       </c>
@@ -12645,7 +12875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4">
       <c r="A138">
         <v>5</v>
       </c>
@@ -12659,7 +12889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4">
       <c r="A139">
         <v>5</v>
       </c>
@@ -12673,7 +12903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4">
       <c r="A140">
         <v>5</v>
       </c>
@@ -12687,7 +12917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4">
       <c r="A141">
         <v>5</v>
       </c>
@@ -12701,7 +12931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4">
       <c r="A142">
         <v>5</v>
       </c>
@@ -12715,7 +12945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4">
       <c r="A143">
         <v>5</v>
       </c>
@@ -12729,7 +12959,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4">
       <c r="A144">
         <v>5</v>
       </c>
@@ -12743,7 +12973,7 @@
         <v>0.39000000000000024</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4">
       <c r="A145">
         <v>5</v>
       </c>
@@ -12757,7 +12987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4">
       <c r="A146">
         <v>5</v>
       </c>
@@ -12771,7 +13001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4">
       <c r="A147">
         <v>5</v>
       </c>
@@ -12785,7 +13015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4">
       <c r="A148">
         <v>5</v>
       </c>
@@ -12799,7 +13029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4">
       <c r="A149">
         <v>5</v>
       </c>
@@ -12813,7 +13043,7 @@
         <v>0.94500000000000073</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4">
       <c r="A150">
         <v>5</v>
       </c>
@@ -12827,7 +13057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4">
       <c r="A151">
         <v>5</v>
       </c>
@@ -12841,7 +13071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4">
       <c r="A152">
         <v>5</v>
       </c>
@@ -12855,7 +13085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4">
       <c r="A153">
         <v>5</v>
       </c>
@@ -12869,7 +13099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4">
       <c r="A154">
         <v>5</v>
       </c>
@@ -12883,7 +13113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4">
       <c r="A155">
         <v>5</v>
       </c>
@@ -12897,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4">
       <c r="A156">
         <v>5</v>
       </c>
@@ -12911,7 +13141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4">
       <c r="A157">
         <v>5</v>
       </c>
@@ -12925,7 +13155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4">
       <c r="A158">
         <v>5</v>
       </c>
@@ -12939,7 +13169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4">
       <c r="A159">
         <v>5</v>
       </c>
@@ -12953,7 +13183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4">
       <c r="A160">
         <v>5</v>
       </c>
@@ -12967,7 +13197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4">
       <c r="A161">
         <v>5</v>
       </c>
@@ -12981,7 +13211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4">
       <c r="A162">
         <v>5</v>
       </c>
@@ -12995,7 +13225,7 @@
         <v>0.32500000000000018</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4">
       <c r="A163">
         <v>5</v>
       </c>
@@ -13009,7 +13239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4">
       <c r="A164">
         <v>5</v>
       </c>
@@ -13023,7 +13253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4">
       <c r="A165">
         <v>5</v>
       </c>
@@ -13037,7 +13267,7 @@
         <v>0.30500000000000016</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4">
       <c r="A166">
         <v>5</v>
       </c>
@@ -13051,7 +13281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4">
       <c r="A167">
         <v>5</v>
       </c>
@@ -13065,7 +13295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4">
       <c r="A168">
         <v>5</v>
       </c>
@@ -13079,7 +13309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4">
       <c r="A169">
         <v>5</v>
       </c>
@@ -13093,7 +13323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4">
       <c r="A170">
         <v>5</v>
       </c>
@@ -13107,7 +13337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4">
       <c r="A171">
         <v>5</v>
       </c>
@@ -13121,7 +13351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4">
       <c r="A172">
         <v>5</v>
       </c>
@@ -13135,7 +13365,7 @@
         <v>0.15500000000000005</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4">
       <c r="A173">
         <v>5</v>
       </c>
@@ -13149,7 +13379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4">
       <c r="A174">
         <v>5</v>
       </c>
@@ -13163,7 +13393,7 @@
         <v>0.40000000000000024</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4">
       <c r="A175">
         <v>5</v>
       </c>
@@ -13177,7 +13407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4">
       <c r="A176">
         <v>5</v>
       </c>
@@ -13191,7 +13421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4">
       <c r="A177">
         <v>5</v>
       </c>
@@ -13205,7 +13435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4">
       <c r="A178">
         <v>5</v>
       </c>
@@ -13219,7 +13449,7 @@
         <v>0.39000000000000024</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4">
       <c r="A179">
         <v>5</v>
       </c>
@@ -13233,7 +13463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4">
       <c r="A180">
         <v>5</v>
       </c>
@@ -13247,7 +13477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4">
       <c r="A181">
         <v>5</v>
       </c>
@@ -13261,7 +13491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4">
       <c r="A182">
         <v>5</v>
       </c>
@@ -13275,7 +13505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4">
       <c r="A183">
         <v>5</v>
       </c>
@@ -13289,7 +13519,7 @@
         <v>0.21500000000000005</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4">
       <c r="A184">
         <v>5</v>
       </c>
@@ -13303,7 +13533,7 @@
         <v>1.5049999999999899</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4">
       <c r="A185">
         <v>5</v>
       </c>
@@ -13317,7 +13547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4">
       <c r="A186">
         <v>5</v>
       </c>
@@ -13331,7 +13561,7 @@
         <v>1.8149999999999833</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4">
       <c r="A187">
         <v>5</v>
       </c>
@@ -13345,7 +13575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4">
       <c r="A188">
         <v>5</v>
       </c>
@@ -13359,7 +13589,7 @@
         <v>2.0949999999999775</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4">
       <c r="A189">
         <v>5</v>
       </c>
@@ -13373,7 +13603,7 @@
         <v>0.39000000000000024</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4">
       <c r="A190">
         <v>5</v>
       </c>
@@ -13387,7 +13617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4">
       <c r="A191">
         <v>5</v>
       </c>
@@ -13401,7 +13631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4">
       <c r="A192">
         <v>6</v>
       </c>
@@ -13415,7 +13645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4">
       <c r="A193">
         <v>6</v>
       </c>
@@ -13429,7 +13659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4">
       <c r="A194">
         <v>6</v>
       </c>
@@ -13443,7 +13673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4">
       <c r="A195">
         <v>6</v>
       </c>
@@ -13457,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4">
       <c r="A196">
         <v>6</v>
       </c>
@@ -13471,7 +13701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4">
       <c r="A197">
         <v>6</v>
       </c>
@@ -13485,7 +13715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4">
       <c r="A198">
         <v>6</v>
       </c>
@@ -13499,7 +13729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4">
       <c r="A199">
         <v>6</v>
       </c>
@@ -13513,7 +13743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4">
       <c r="A200">
         <v>6</v>
       </c>
@@ -13527,7 +13757,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4">
       <c r="A201">
         <v>6</v>
       </c>
@@ -13541,7 +13771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4">
       <c r="A202">
         <v>6</v>
       </c>
@@ -13555,7 +13785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4">
       <c r="A203">
         <v>6</v>
       </c>
@@ -13569,7 +13799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4">
       <c r="A204">
         <v>6</v>
       </c>
@@ -13583,7 +13813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4">
       <c r="A205">
         <v>6</v>
       </c>
@@ -13597,7 +13827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4">
       <c r="A206">
         <v>6</v>
       </c>
@@ -13611,7 +13841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4">
       <c r="A207">
         <v>6</v>
       </c>
@@ -13625,7 +13855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4">
       <c r="A208">
         <v>6</v>
       </c>
@@ -13639,7 +13869,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4">
       <c r="A209">
         <v>6</v>
       </c>
@@ -13653,7 +13883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4">
       <c r="A210">
         <v>6</v>
       </c>
@@ -13667,7 +13897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4">
       <c r="A211">
         <v>6</v>
       </c>
@@ -13681,7 +13911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4">
       <c r="A212">
         <v>6</v>
       </c>
@@ -13695,7 +13925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4">
       <c r="A213">
         <v>6</v>
       </c>
@@ -13709,7 +13939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4">
       <c r="A214">
         <v>6</v>
       </c>
@@ -13723,7 +13953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4">
       <c r="A215">
         <v>6</v>
       </c>
@@ -13737,7 +13967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4">
       <c r="A216">
         <v>6</v>
       </c>
@@ -13751,7 +13981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4">
       <c r="A217">
         <v>6</v>
       </c>
@@ -13765,7 +13995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4">
       <c r="A218">
         <v>6</v>
       </c>
@@ -13779,7 +14009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4">
       <c r="A219">
         <v>6</v>
       </c>
@@ -13793,7 +14023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4">
       <c r="A220">
         <v>6</v>
       </c>
@@ -13807,7 +14037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4">
       <c r="A221">
         <v>6</v>
       </c>
@@ -13821,7 +14051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4">
       <c r="A222">
         <v>6</v>
       </c>
@@ -13835,7 +14065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4">
       <c r="A223">
         <v>6</v>
       </c>
@@ -13849,7 +14079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4">
       <c r="A224">
         <v>6</v>
       </c>
@@ -13863,7 +14093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4">
       <c r="A225">
         <v>6</v>
       </c>
@@ -13877,7 +14107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4">
       <c r="A226">
         <v>6</v>
       </c>
@@ -13891,7 +14121,7 @@
         <v>0.40500000000000025</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4">
       <c r="A227">
         <v>6</v>
       </c>
@@ -13905,7 +14135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4">
       <c r="A228">
         <v>6</v>
       </c>
@@ -13919,7 +14149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4">
       <c r="A229">
         <v>6</v>
       </c>
@@ -13933,7 +14163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4">
       <c r="A230">
         <v>6</v>
       </c>
@@ -13947,7 +14177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4">
       <c r="A231">
         <v>6</v>
       </c>
@@ -13961,7 +14191,7 @@
         <v>0.40000000000000024</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4">
       <c r="A232">
         <v>6</v>
       </c>
@@ -13975,7 +14205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4">
       <c r="A233">
         <v>6</v>
       </c>
@@ -13989,7 +14219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4">
       <c r="A234">
         <v>6</v>
       </c>
@@ -14003,7 +14233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4">
       <c r="A235">
         <v>6</v>
       </c>
@@ -14017,7 +14247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4">
       <c r="A236">
         <v>6</v>
       </c>
@@ -14031,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4">
       <c r="A237">
         <v>6</v>
       </c>
@@ -14045,7 +14275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4">
       <c r="A238">
         <v>6</v>
       </c>
@@ -14059,7 +14289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4">
       <c r="A239">
         <v>6</v>
       </c>
@@ -14073,7 +14303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4">
       <c r="A240">
         <v>6</v>
       </c>
@@ -14087,7 +14317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4">
       <c r="A241">
         <v>6</v>
       </c>
@@ -14101,7 +14331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4">
       <c r="A242">
         <v>6</v>
       </c>
@@ -14115,7 +14345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4">
       <c r="A243">
         <v>6</v>
       </c>
@@ -14129,7 +14359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4">
       <c r="A244">
         <v>6</v>
       </c>
@@ -14143,7 +14373,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4">
       <c r="A245">
         <v>6</v>
       </c>
@@ -14157,7 +14387,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4">
       <c r="A246">
         <v>6</v>
       </c>
@@ -14171,7 +14401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4">
       <c r="A247">
         <v>6</v>
       </c>
@@ -14185,7 +14415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4">
       <c r="A248">
         <v>6</v>
       </c>
@@ -14199,7 +14429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4">
       <c r="A249">
         <v>6</v>
       </c>
@@ -14213,7 +14443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4">
       <c r="A250">
         <v>6</v>
       </c>
@@ -14227,7 +14457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4">
       <c r="A251">
         <v>6</v>
       </c>
@@ -14241,7 +14471,7 @@
         <v>1.3850000000000011</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4">
       <c r="A252">
         <v>6</v>
       </c>
@@ -14255,7 +14485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4">
       <c r="A253">
         <v>6</v>
       </c>
@@ -14269,7 +14499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4">
       <c r="A254">
         <v>6</v>
       </c>
@@ -14283,7 +14513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4">
       <c r="A255">
         <v>6</v>
       </c>
@@ -14297,7 +14527,7 @@
         <v>4.9999999999999996E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4">
       <c r="A256">
         <v>6</v>
       </c>
@@ -14311,7 +14541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4">
       <c r="A257">
         <v>6</v>
       </c>
@@ -14325,7 +14555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4">
       <c r="A258">
         <v>6</v>
       </c>
@@ -14339,7 +14569,7 @@
         <v>0.22500000000000012</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4">
       <c r="A259">
         <v>6</v>
       </c>
@@ -14353,7 +14583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4">
       <c r="A260">
         <v>6</v>
       </c>
@@ -14367,7 +14597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4">
       <c r="A261">
         <v>6</v>
       </c>
@@ -14381,7 +14611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4">
       <c r="A262">
         <v>6</v>
       </c>
@@ -14395,7 +14625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4">
       <c r="A263">
         <v>6</v>
       </c>
@@ -14409,7 +14639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4">
       <c r="A264">
         <v>6</v>
       </c>
@@ -14423,7 +14653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4">
       <c r="A265">
         <v>6</v>
       </c>
@@ -14437,7 +14667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4">
       <c r="A266">
         <v>6</v>
       </c>
@@ -14451,7 +14681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4">
       <c r="A267">
         <v>6</v>
       </c>
@@ -14465,7 +14695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4">
       <c r="A268">
         <v>6</v>
       </c>
@@ -14479,7 +14709,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4">
       <c r="A269">
         <v>6</v>
       </c>
@@ -14493,7 +14723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4">
       <c r="A270">
         <v>6</v>
       </c>
@@ -14507,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4">
       <c r="A271">
         <v>6</v>
       </c>
@@ -14521,7 +14751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4">
       <c r="A272">
         <v>6</v>
       </c>
@@ -14535,7 +14765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4">
       <c r="A273">
         <v>6</v>
       </c>
@@ -14549,7 +14779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4">
       <c r="A274">
         <v>6</v>
       </c>
@@ -14563,7 +14793,7 @@
         <v>0.60500000000000043</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4">
       <c r="A275">
         <v>6</v>
       </c>
@@ -14577,7 +14807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4">
       <c r="A276">
         <v>6</v>
       </c>
@@ -14591,7 +14821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4">
       <c r="A277">
         <v>6</v>
       </c>
@@ -14605,7 +14835,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4">
       <c r="A278">
         <v>6</v>
       </c>
@@ -14619,7 +14849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4">
       <c r="A279">
         <v>6</v>
       </c>
@@ -14633,7 +14863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4">
       <c r="A280">
         <v>6</v>
       </c>
@@ -14647,7 +14877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4">
       <c r="A281">
         <v>6</v>
       </c>
@@ -14661,7 +14891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4">
       <c r="A282">
         <v>6</v>
       </c>
@@ -14675,7 +14905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4">
       <c r="A283">
         <v>6</v>
       </c>
@@ -14689,7 +14919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4">
       <c r="A284">
         <v>6</v>
       </c>
@@ -14703,7 +14933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4">
       <c r="A285">
         <v>6</v>
       </c>
@@ -14717,7 +14947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4">
       <c r="A286">
         <v>6</v>
       </c>
@@ -14731,7 +14961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4">
       <c r="A287">
         <v>6</v>
       </c>
@@ -14745,7 +14975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4">
       <c r="A288">
         <v>6</v>
       </c>
@@ -14759,7 +14989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4">
       <c r="A289">
         <v>6</v>
       </c>
@@ -14773,7 +15003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4">
       <c r="A290">
         <v>6</v>
       </c>
@@ -14787,7 +15017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4">
       <c r="A291">
         <v>6</v>
       </c>
@@ -14801,7 +15031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4">
       <c r="A292">
         <v>6</v>
       </c>
@@ -14815,7 +15045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4">
       <c r="A293">
         <v>6</v>
       </c>
@@ -14829,7 +15059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4">
       <c r="A294">
         <v>6</v>
       </c>
@@ -14843,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4">
       <c r="A295">
         <v>6</v>
       </c>
@@ -14857,7 +15087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4">
       <c r="A296">
         <v>6</v>
       </c>
@@ -14871,7 +15101,7 @@
         <v>0.60000000000000042</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4">
       <c r="A297">
         <v>6</v>
       </c>
@@ -14885,7 +15115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4">
       <c r="A298">
         <v>6</v>
       </c>
@@ -14899,7 +15129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4">
       <c r="A299">
         <v>6</v>
       </c>
@@ -14913,7 +15143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4">
       <c r="A300">
         <v>6</v>
       </c>
@@ -14927,7 +15157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4">
       <c r="A301">
         <v>6</v>
       </c>
@@ -14941,7 +15171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4">
       <c r="A302">
         <v>6</v>
       </c>
@@ -14955,7 +15185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4">
       <c r="A303">
         <v>6</v>
       </c>
@@ -14969,7 +15199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4">
       <c r="A304">
         <v>6</v>
       </c>
@@ -14983,7 +15213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4">
       <c r="A305">
         <v>6</v>
       </c>
@@ -14997,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4">
       <c r="A306">
         <v>6</v>
       </c>
@@ -15011,7 +15241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4">
       <c r="A307">
         <v>6</v>
       </c>
@@ -15025,7 +15255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4">
       <c r="A308">
         <v>6</v>
       </c>
@@ -15039,7 +15269,7 @@
         <v>0.65500000000000047</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4">
       <c r="A309">
         <v>6</v>
       </c>
@@ -15053,7 +15283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4">
       <c r="A310">
         <v>6</v>
       </c>
@@ -15067,7 +15297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4">
       <c r="A311">
         <v>6</v>
       </c>
@@ -15081,7 +15311,7 @@
         <v>0.96500000000000064</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4">
       <c r="A312">
         <v>6</v>
       </c>
@@ -15095,7 +15325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4">
       <c r="A313">
         <v>6</v>
       </c>
@@ -15109,7 +15339,7 @@
         <v>1.370000000000001</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4">
       <c r="A314">
         <v>6</v>
       </c>
@@ -15123,7 +15353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4">
       <c r="A315">
         <v>6</v>
       </c>
@@ -15137,7 +15367,7 @@
         <v>1.2999999999999943</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4">
       <c r="A316">
         <v>6</v>
       </c>
@@ -15151,7 +15381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4">
       <c r="A317">
         <v>6</v>
       </c>
@@ -15165,7 +15395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4">
       <c r="A318">
         <v>6</v>
       </c>
@@ -15179,7 +15409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4">
       <c r="A319">
         <v>6</v>
       </c>
@@ -15193,7 +15423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4">
       <c r="A320">
         <v>6</v>
       </c>
@@ -15207,7 +15437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4">
       <c r="A321">
         <v>6</v>
       </c>
@@ -15221,7 +15451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4">
       <c r="A322">
         <v>6</v>
       </c>
@@ -15235,7 +15465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4">
       <c r="A323">
         <v>6</v>
       </c>
@@ -15249,7 +15479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4">
       <c r="A324">
         <v>6</v>
       </c>
@@ -15263,7 +15493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4">
       <c r="A325">
         <v>6</v>
       </c>
@@ -15277,7 +15507,7 @@
         <v>0.32500000000000018</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4">
       <c r="A326">
         <v>6</v>
       </c>
@@ -15291,7 +15521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4">
       <c r="A327">
         <v>6</v>
       </c>
@@ -15305,7 +15535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4">
       <c r="A328">
         <v>6</v>
       </c>
@@ -15319,7 +15549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4">
       <c r="A329">
         <v>6</v>
       </c>
@@ -15333,7 +15563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4">
       <c r="A330">
         <v>6</v>
       </c>
@@ -15347,7 +15577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4">
       <c r="A331">
         <v>6</v>
       </c>
@@ -15361,7 +15591,7 @@
         <v>0.44500000000000028</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4">
       <c r="A332">
         <v>6</v>
       </c>
@@ -15375,7 +15605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4">
       <c r="A333">
         <v>6</v>
       </c>
@@ -15389,7 +15619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4">
       <c r="A334">
         <v>6</v>
       </c>
@@ -15403,7 +15633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4">
       <c r="A335">
         <v>6</v>
       </c>
@@ -15417,7 +15647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4">
       <c r="A336">
         <v>6</v>
       </c>
@@ -15431,7 +15661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4">
       <c r="A337">
         <v>6</v>
       </c>
@@ -15445,7 +15675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4">
       <c r="A338">
         <v>6</v>
       </c>
@@ -15459,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4">
       <c r="A339">
         <v>6</v>
       </c>
@@ -15473,7 +15703,7 @@
         <v>2.0799999999999779</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4">
       <c r="A340">
         <v>6</v>
       </c>
@@ -15487,7 +15717,7 @@
         <v>0.33500000000000019</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4">
       <c r="A341">
         <v>6</v>
       </c>
@@ -15501,7 +15731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4">
       <c r="A342">
         <v>7</v>
       </c>
@@ -15515,7 +15745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4">
       <c r="A343">
         <v>7</v>
       </c>
@@ -15529,7 +15759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4">
       <c r="A344">
         <v>7</v>
       </c>
@@ -15543,7 +15773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4">
       <c r="A345">
         <v>7</v>
       </c>
@@ -15557,7 +15787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4">
       <c r="A346">
         <v>7</v>
       </c>
@@ -15571,7 +15801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4">
       <c r="A347">
         <v>7</v>
       </c>
@@ -15585,7 +15815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4">
       <c r="A348">
         <v>7</v>
       </c>
@@ -15599,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4">
       <c r="A349">
         <v>7</v>
       </c>
@@ -15613,7 +15843,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4">
       <c r="A350">
         <v>7</v>
       </c>
@@ -15627,7 +15857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4">
       <c r="A351">
         <v>7</v>
       </c>
@@ -15641,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4">
       <c r="A352">
         <v>7</v>
       </c>
@@ -15655,7 +15885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4">
       <c r="A353">
         <v>7</v>
       </c>
@@ -15669,7 +15899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4">
       <c r="A354">
         <v>7</v>
       </c>
@@ -15683,7 +15913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4">
       <c r="A355">
         <v>7</v>
       </c>
@@ -15697,7 +15927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4">
       <c r="A356">
         <v>7</v>
       </c>
@@ -15711,7 +15941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4">
       <c r="A357">
         <v>7</v>
       </c>
@@ -15725,7 +15955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4">
       <c r="A358">
         <v>7</v>
       </c>
@@ -15739,7 +15969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4">
       <c r="A359">
         <v>7</v>
       </c>
@@ -15753,7 +15983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4">
       <c r="A360">
         <v>7</v>
       </c>
@@ -15767,7 +15997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4">
       <c r="A361">
         <v>7</v>
       </c>
@@ -15781,7 +16011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4">
       <c r="A362">
         <v>7</v>
       </c>
@@ -15795,7 +16025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4">
       <c r="A363">
         <v>7</v>
       </c>
@@ -15809,7 +16039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4">
       <c r="A364">
         <v>7</v>
       </c>
@@ -15823,7 +16053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4">
       <c r="A365">
         <v>7</v>
       </c>
@@ -15837,7 +16067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4">
       <c r="A366">
         <v>7</v>
       </c>
@@ -15851,7 +16081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4">
       <c r="A367">
         <v>7</v>
       </c>
@@ -15865,7 +16095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4">
       <c r="A368">
         <v>7</v>
       </c>
@@ -15879,7 +16109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4">
       <c r="A369">
         <v>7</v>
       </c>
@@ -15893,7 +16123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4">
       <c r="A370">
         <v>7</v>
       </c>
@@ -15907,7 +16137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4">
       <c r="A371">
         <v>7</v>
       </c>
@@ -15921,7 +16151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4">
       <c r="A372">
         <v>7</v>
       </c>
@@ -15935,7 +16165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4">
       <c r="A373">
         <v>7</v>
       </c>
@@ -15949,7 +16179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4">
       <c r="A374">
         <v>7</v>
       </c>
@@ -15963,7 +16193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4">
       <c r="A375">
         <v>7</v>
       </c>
@@ -15977,7 +16207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4">
       <c r="A376">
         <v>7</v>
       </c>
@@ -15991,7 +16221,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4">
       <c r="A377">
         <v>7</v>
       </c>
@@ -16005,7 +16235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4">
       <c r="A378">
         <v>7</v>
       </c>
@@ -16019,7 +16249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4">
       <c r="A379">
         <v>7</v>
       </c>
@@ -16033,7 +16263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4">
       <c r="A380">
         <v>7</v>
       </c>
@@ -16047,7 +16277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4">
       <c r="A381">
         <v>7</v>
       </c>
@@ -16061,7 +16291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4">
       <c r="A382">
         <v>7</v>
       </c>
@@ -16075,7 +16305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4">
       <c r="A383">
         <v>7</v>
       </c>
@@ -16089,7 +16319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4">
       <c r="A384">
         <v>7</v>
       </c>
@@ -16103,7 +16333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4">
       <c r="A385">
         <v>7</v>
       </c>
@@ -16117,7 +16347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4">
       <c r="A386">
         <v>7</v>
       </c>
@@ -16131,7 +16361,7 @@
         <v>0.41500000000000026</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4">
       <c r="A387">
         <v>7</v>
       </c>
@@ -16145,7 +16375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4">
       <c r="A388">
         <v>7</v>
       </c>
@@ -16159,7 +16389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4">
       <c r="A389">
         <v>7</v>
       </c>
@@ -16173,7 +16403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4">
       <c r="A390">
         <v>7</v>
       </c>
@@ -16187,7 +16417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4">
       <c r="A391">
         <v>7</v>
       </c>
@@ -16201,7 +16431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4">
       <c r="A392">
         <v>7</v>
       </c>
@@ -16215,7 +16445,7 @@
         <v>1.6199999999999875</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4">
       <c r="A393">
         <v>7</v>
       </c>
@@ -16229,7 +16459,7 @@
         <v>1.1949999999999965</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4">
       <c r="A394">
         <v>7</v>
       </c>
@@ -16243,7 +16473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4">
       <c r="A395">
         <v>7</v>
       </c>
@@ -16257,7 +16487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4">
       <c r="A396">
         <v>7</v>
       </c>
@@ -16271,7 +16501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4">
       <c r="A397">
         <v>7</v>
       </c>
@@ -16285,7 +16515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4">
       <c r="A398">
         <v>7</v>
       </c>
@@ -16299,7 +16529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4">
       <c r="A399">
         <v>7</v>
       </c>
@@ -16313,7 +16543,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4">
       <c r="A400">
         <v>7</v>
       </c>
@@ -16327,7 +16557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4">
       <c r="A401">
         <v>7</v>
       </c>
@@ -16341,7 +16571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4">
       <c r="A402">
         <v>7</v>
       </c>
@@ -16355,7 +16585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4">
       <c r="A403">
         <v>7</v>
       </c>
@@ -16369,7 +16599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4">
       <c r="A404">
         <v>7</v>
       </c>
@@ -16383,7 +16613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4">
       <c r="A405">
         <v>7</v>
       </c>
@@ -16397,7 +16627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4">
       <c r="A406">
         <v>7</v>
       </c>
@@ -16411,7 +16641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4">
       <c r="A407">
         <v>7</v>
       </c>
@@ -16425,7 +16655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4">
       <c r="A408">
         <v>7</v>
       </c>
@@ -16439,7 +16669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4">
       <c r="A409">
         <v>7</v>
       </c>
@@ -16453,7 +16683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4">
       <c r="A410">
         <v>7</v>
       </c>
@@ -16467,7 +16697,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4">
       <c r="A411">
         <v>7</v>
       </c>
@@ -16481,7 +16711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4">
       <c r="A412">
         <v>7</v>
       </c>
@@ -16495,7 +16725,7 @@
         <v>0.26000000000000012</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4">
       <c r="A413">
         <v>7</v>
       </c>
@@ -16509,7 +16739,7 @@
         <v>1.3399999999999934</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4">
       <c r="A414">
         <v>7</v>
       </c>
@@ -16523,7 +16753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4">
       <c r="A415">
         <v>7</v>
       </c>
@@ -16537,7 +16767,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4">
       <c r="A416">
         <v>7</v>
       </c>
@@ -16551,7 +16781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4">
       <c r="A417">
         <v>7</v>
       </c>
@@ -16565,7 +16795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4">
       <c r="A418">
         <v>7</v>
       </c>
@@ -16579,7 +16809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4">
       <c r="A419">
         <v>7</v>
       </c>
@@ -16593,7 +16823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4">
       <c r="A420">
         <v>7</v>
       </c>
@@ -16607,7 +16837,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4">
       <c r="A421">
         <v>7</v>
       </c>
@@ -16621,7 +16851,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4">
       <c r="A422">
         <v>7</v>
       </c>
@@ -16635,7 +16865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4">
       <c r="A423">
         <v>7</v>
       </c>
@@ -16649,7 +16879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4">
       <c r="A424">
         <v>7</v>
       </c>
@@ -16663,7 +16893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4">
       <c r="A425">
         <v>7</v>
       </c>
@@ -16677,7 +16907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4">
       <c r="A426">
         <v>7</v>
       </c>
@@ -16691,7 +16921,7 @@
         <v>0.14500000000000005</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4">
       <c r="A427">
         <v>7</v>
       </c>
@@ -16705,7 +16935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4">
       <c r="A428">
         <v>7</v>
       </c>
@@ -16719,7 +16949,7 @@
         <v>0.5700000000000004</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4">
       <c r="A429">
         <v>7</v>
       </c>
@@ -16733,7 +16963,7 @@
         <v>0.16000000000000006</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4">
       <c r="A430">
         <v>7</v>
       </c>
@@ -16747,7 +16977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4">
       <c r="A431">
         <v>7</v>
       </c>
@@ -16761,7 +16991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4">
       <c r="A432">
         <v>7</v>
       </c>
@@ -16775,7 +17005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4">
       <c r="A433">
         <v>7</v>
       </c>
@@ -16789,7 +17019,7 @@
         <v>0.10000000000000002</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4">
       <c r="A434">
         <v>7</v>
       </c>
@@ -16803,7 +17033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4">
       <c r="A435">
         <v>7</v>
       </c>
@@ -16817,7 +17047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4">
       <c r="A436">
         <v>7</v>
       </c>
@@ -16831,7 +17061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4">
       <c r="A437">
         <v>7</v>
       </c>
@@ -16845,7 +17075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4">
       <c r="A438">
         <v>7</v>
       </c>
@@ -16859,7 +17089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4">
       <c r="A439">
         <v>7</v>
       </c>
@@ -16873,7 +17103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4">
       <c r="A440">
         <v>7</v>
       </c>
@@ -16887,7 +17117,7 @@
         <v>0.97500000000000064</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4">
       <c r="A441">
         <v>7</v>
       </c>
@@ -16901,7 +17131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4">
       <c r="A442">
         <v>7</v>
       </c>
@@ -16915,7 +17145,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4">
       <c r="A443">
         <v>7</v>
       </c>
@@ -16929,7 +17159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4">
       <c r="A444">
         <v>7</v>
       </c>
@@ -16943,7 +17173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4">
       <c r="A445">
         <v>7</v>
       </c>
@@ -16957,7 +17187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4">
       <c r="A446">
         <v>7</v>
       </c>
@@ -16971,7 +17201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4">
       <c r="A447">
         <v>7</v>
       </c>
@@ -16985,7 +17215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4">
       <c r="A448">
         <v>7</v>
       </c>
@@ -16999,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4">
       <c r="A449">
         <v>7</v>
       </c>
@@ -17013,7 +17243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4">
       <c r="A450">
         <v>7</v>
       </c>
@@ -17027,7 +17257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4">
       <c r="A451">
         <v>7</v>
       </c>
@@ -17041,7 +17271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4">
       <c r="A452">
         <v>8</v>
       </c>
@@ -17055,7 +17285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4">
       <c r="A453">
         <v>8</v>
       </c>
@@ -17069,7 +17299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4">
       <c r="A454">
         <v>8</v>
       </c>
@@ -17083,7 +17313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4">
       <c r="A455">
         <v>8</v>
       </c>
@@ -17097,7 +17327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4">
       <c r="A456">
         <v>8</v>
       </c>
@@ -17111,7 +17341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4">
       <c r="A457">
         <v>8</v>
       </c>
@@ -17125,7 +17355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4">
       <c r="A458">
         <v>8</v>
       </c>
@@ -17139,7 +17369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4">
       <c r="A459">
         <v>8</v>
       </c>
@@ -17153,7 +17383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4">
       <c r="A460">
         <v>8</v>
       </c>
@@ -17167,7 +17397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4">
       <c r="A461">
         <v>8</v>
       </c>
@@ -17181,7 +17411,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4">
       <c r="A462">
         <v>8</v>
       </c>
@@ -17195,7 +17425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4">
       <c r="A463">
         <v>8</v>
       </c>
@@ -17209,7 +17439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4">
       <c r="A464">
         <v>8</v>
       </c>
@@ -17223,7 +17453,7 @@
         <v>0.39000000000000024</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4">
       <c r="A465">
         <v>8</v>
       </c>
@@ -17237,7 +17467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4">
       <c r="A466">
         <v>8</v>
       </c>
@@ -17251,7 +17481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4">
       <c r="A467">
         <v>8</v>
       </c>
@@ -17265,7 +17495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4">
       <c r="A468">
         <v>8</v>
       </c>
@@ -17279,7 +17509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4">
       <c r="A469">
         <v>8</v>
       </c>
@@ -17293,7 +17523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4">
       <c r="A470">
         <v>8</v>
       </c>
@@ -17307,7 +17537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4">
       <c r="A471">
         <v>8</v>
       </c>
@@ -17321,7 +17551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4">
       <c r="A472">
         <v>8</v>
       </c>
@@ -17335,7 +17565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4">
       <c r="A473">
         <v>8</v>
       </c>
@@ -17349,7 +17579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4">
       <c r="A474">
         <v>8</v>
       </c>
@@ -17363,7 +17593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4">
       <c r="A475">
         <v>8</v>
       </c>
@@ -17377,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4">
       <c r="A476">
         <v>8</v>
       </c>
@@ -17391,7 +17621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4">
       <c r="A477">
         <v>8</v>
       </c>
@@ -17405,7 +17635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4">
       <c r="A478">
         <v>8</v>
       </c>
@@ -17419,7 +17649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4">
       <c r="A479">
         <v>8</v>
       </c>
@@ -17433,7 +17663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4">
       <c r="A480">
         <v>8</v>
       </c>
@@ -17447,7 +17677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4">
       <c r="A481">
         <v>8</v>
       </c>
@@ -17461,7 +17691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4">
       <c r="A482">
         <v>8</v>
       </c>
@@ -17475,7 +17705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4">
       <c r="A483">
         <v>8</v>
       </c>
@@ -17489,7 +17719,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4">
       <c r="A484">
         <v>8</v>
       </c>
@@ -17503,7 +17733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4">
       <c r="A485">
         <v>8</v>
       </c>
@@ -17517,7 +17747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4">
       <c r="A486">
         <v>8</v>
       </c>
@@ -17531,7 +17761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4">
       <c r="A487">
         <v>8</v>
       </c>
@@ -17545,7 +17775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4">
       <c r="A488">
         <v>8</v>
       </c>
@@ -17559,7 +17789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4">
       <c r="A489">
         <v>8</v>
       </c>
@@ -17573,7 +17803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4">
       <c r="A490">
         <v>8</v>
       </c>
@@ -17587,7 +17817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4">
       <c r="A491">
         <v>8</v>
       </c>
@@ -17601,7 +17831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4">
       <c r="A492">
         <v>8</v>
       </c>
@@ -17615,7 +17845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4">
       <c r="A493">
         <v>8</v>
       </c>
@@ -17629,7 +17859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4">
       <c r="A494">
         <v>8</v>
       </c>
@@ -17643,7 +17873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4">
       <c r="A495">
         <v>8</v>
       </c>
@@ -17657,7 +17887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4">
       <c r="A496">
         <v>8</v>
       </c>
@@ -17671,7 +17901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4">
       <c r="A497">
         <v>8</v>
       </c>
@@ -17685,7 +17915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4">
       <c r="A498">
         <v>8</v>
       </c>
@@ -17699,7 +17929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4">
       <c r="A499">
         <v>8</v>
       </c>
@@ -17713,7 +17943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4">
       <c r="A500">
         <v>8</v>
       </c>
@@ -17727,7 +17957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4">
       <c r="A501">
         <v>8</v>
       </c>
